--- a/InputData/bldgs/CiDESCTY/Change in Distribued Electricity Source Capacities This Year.xlsx
+++ b/InputData/bldgs/CiDESCTY/Change in Distribued Electricity Source Capacities This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\claude-aeo-2026\input data\bldgs\CiDESCTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\CiDESCTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3004A51C-3B5D-4DFE-9E91-BE844A9972D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0F80FA-6293-47D2-8B70-32355C726993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="714" firstSheet="12" activeTab="13" xr2:uid="{78C42925-BD2F-4DDC-9C55-3AA1D702B622}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" tabRatio="714" firstSheet="12" activeTab="16" xr2:uid="{78C42925-BD2F-4DDC-9C55-3AA1D702B622}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -29,14 +29,15 @@
     <sheet name="CiDESCTY-urban-residential" sheetId="26" r:id="rId14"/>
     <sheet name="CiDESCTY-rural-residential" sheetId="27" r:id="rId15"/>
     <sheet name="CiDESCTY-commercial" sheetId="28" r:id="rId16"/>
-    <sheet name="AEO26_Table_22._Commercial" sheetId="30" r:id="rId17"/>
-    <sheet name="AEO26_Table_21._Residential" sheetId="29" r:id="rId18"/>
+    <sheet name="CiDESCTY-data-centers" sheetId="31" r:id="rId17"/>
+    <sheet name="AEO26_Table_22._Commercial" sheetId="30" r:id="rId18"/>
+    <sheet name="AEO26_Table_21._Residential" sheetId="29" r:id="rId19"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId19"/>
     <externalReference r:id="rId20"/>
     <externalReference r:id="rId21"/>
     <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
   </externalReferences>
   <definedNames>
     <definedName name="billion_kw_to_MW">About!$B$30</definedName>
@@ -66,6 +67,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -73,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2615" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2642" uniqueCount="1082">
   <si>
     <t>Energy Information Administration</t>
   </si>
@@ -3460,6 +3464,12 @@
   </si>
   <si>
     <t>Commercial: Combined Heat and Power: Energy Input: Total: Alternative Electricity and Transportation</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. There are no policy-mandated changes in distributed capacity at data centers, so their export tab is zero.</t>
   </si>
 </sst>
 </file>
@@ -4254,7 +4264,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4388,10 +4398,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -14004,7 +14012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" customWidth="1"/>
@@ -14159,6 +14167,14 @@
         <v>1000</v>
       </c>
       <c r="F31" s="13"/>
+    </row>
+    <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B33" s="67" t="s">
+        <v>1081</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23637,2163 +23653,2162 @@
   <dimension ref="A1:AB25"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" style="67" customWidth="1"/>
-    <col min="2" max="28" width="9.5703125" style="67" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.7109375" style="67"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="28" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="67">
+      <c r="B1">
         <v>2024</v>
       </c>
-      <c r="C1" s="67">
+      <c r="C1">
         <v>2025</v>
       </c>
-      <c r="D1" s="67">
+      <c r="D1">
         <v>2026</v>
       </c>
-      <c r="E1" s="67">
+      <c r="E1">
         <v>2027</v>
       </c>
-      <c r="F1" s="67">
+      <c r="F1">
         <v>2028</v>
       </c>
-      <c r="G1" s="67">
+      <c r="G1">
         <v>2029</v>
       </c>
-      <c r="H1" s="67">
+      <c r="H1">
         <v>2030</v>
       </c>
-      <c r="I1" s="67">
+      <c r="I1">
         <v>2031</v>
       </c>
-      <c r="J1" s="67">
+      <c r="J1">
         <v>2032</v>
       </c>
-      <c r="K1" s="67">
+      <c r="K1">
         <v>2033</v>
       </c>
-      <c r="L1" s="67">
+      <c r="L1">
         <v>2034</v>
       </c>
-      <c r="M1" s="67">
+      <c r="M1">
         <v>2035</v>
       </c>
-      <c r="N1" s="67">
+      <c r="N1">
         <v>2036</v>
       </c>
-      <c r="O1" s="67">
+      <c r="O1">
         <v>2037</v>
       </c>
-      <c r="P1" s="67">
+      <c r="P1">
         <v>2038</v>
       </c>
-      <c r="Q1" s="67">
+      <c r="Q1">
         <v>2039</v>
       </c>
-      <c r="R1" s="67">
+      <c r="R1">
         <v>2040</v>
       </c>
-      <c r="S1" s="67">
+      <c r="S1">
         <v>2041</v>
       </c>
-      <c r="T1" s="67">
+      <c r="T1">
         <v>2042</v>
       </c>
-      <c r="U1" s="67">
+      <c r="U1">
         <v>2043</v>
       </c>
-      <c r="V1" s="67">
+      <c r="V1">
         <v>2044</v>
       </c>
-      <c r="W1" s="67">
+      <c r="W1">
         <v>2045</v>
       </c>
-      <c r="X1" s="67">
+      <c r="X1">
         <v>2046</v>
       </c>
-      <c r="Y1" s="67">
+      <c r="Y1">
         <v>2047</v>
       </c>
-      <c r="Z1" s="67">
+      <c r="Z1">
         <v>2048</v>
       </c>
-      <c r="AA1" s="67">
+      <c r="AA1">
         <v>2049</v>
       </c>
-      <c r="AB1" s="67">
+      <c r="AB1">
         <v>2050</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="67">
-        <v>0</v>
-      </c>
-      <c r="C2" s="67">
-        <v>0</v>
-      </c>
-      <c r="D2" s="67">
-        <v>0</v>
-      </c>
-      <c r="E2" s="67">
-        <v>0</v>
-      </c>
-      <c r="F2" s="67">
-        <v>0</v>
-      </c>
-      <c r="G2" s="67">
-        <v>0</v>
-      </c>
-      <c r="H2" s="67">
-        <v>0</v>
-      </c>
-      <c r="I2" s="67">
-        <v>0</v>
-      </c>
-      <c r="J2" s="67">
-        <v>0</v>
-      </c>
-      <c r="K2" s="67">
-        <v>0</v>
-      </c>
-      <c r="L2" s="67">
-        <v>0</v>
-      </c>
-      <c r="M2" s="67">
-        <v>0</v>
-      </c>
-      <c r="N2" s="67">
-        <v>0</v>
-      </c>
-      <c r="O2" s="67">
-        <v>0</v>
-      </c>
-      <c r="P2" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="67">
-        <v>0</v>
-      </c>
-      <c r="R2" s="67">
-        <v>0</v>
-      </c>
-      <c r="S2" s="67">
-        <v>0</v>
-      </c>
-      <c r="T2" s="67">
-        <v>0</v>
-      </c>
-      <c r="U2" s="67">
-        <v>0</v>
-      </c>
-      <c r="V2" s="67">
-        <v>0</v>
-      </c>
-      <c r="W2" s="67">
-        <v>0</v>
-      </c>
-      <c r="X2" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="67">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="A3" t="s">
         <v>326</v>
       </c>
-      <c r="B3" s="67">
-        <v>0</v>
-      </c>
-      <c r="C3" s="67">
-        <v>0</v>
-      </c>
-      <c r="D3" s="67">
-        <v>0</v>
-      </c>
-      <c r="E3" s="67">
-        <v>0</v>
-      </c>
-      <c r="F3" s="67">
-        <v>0</v>
-      </c>
-      <c r="G3" s="67">
-        <v>0</v>
-      </c>
-      <c r="H3" s="67">
-        <v>0</v>
-      </c>
-      <c r="I3" s="67">
-        <v>0</v>
-      </c>
-      <c r="J3" s="67">
-        <v>0</v>
-      </c>
-      <c r="K3" s="67">
-        <v>0</v>
-      </c>
-      <c r="L3" s="67">
-        <v>0</v>
-      </c>
-      <c r="M3" s="67">
-        <v>0</v>
-      </c>
-      <c r="N3" s="67">
-        <v>0</v>
-      </c>
-      <c r="O3" s="67">
-        <v>0</v>
-      </c>
-      <c r="P3" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="67">
-        <v>0</v>
-      </c>
-      <c r="R3" s="67">
-        <v>0</v>
-      </c>
-      <c r="S3" s="67">
-        <v>0</v>
-      </c>
-      <c r="T3" s="67">
-        <v>0</v>
-      </c>
-      <c r="U3" s="67">
-        <v>0</v>
-      </c>
-      <c r="V3" s="67">
-        <v>0</v>
-      </c>
-      <c r="W3" s="67">
-        <v>0</v>
-      </c>
-      <c r="X3" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="67">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" t="s">
         <v>327</v>
       </c>
-      <c r="B4" s="67">
-        <v>0</v>
-      </c>
-      <c r="C4" s="67">
-        <v>0</v>
-      </c>
-      <c r="D4" s="67">
-        <v>0</v>
-      </c>
-      <c r="E4" s="67">
-        <v>0</v>
-      </c>
-      <c r="F4" s="67">
-        <v>0</v>
-      </c>
-      <c r="G4" s="67">
-        <v>0</v>
-      </c>
-      <c r="H4" s="67">
-        <v>0</v>
-      </c>
-      <c r="I4" s="67">
-        <v>0</v>
-      </c>
-      <c r="J4" s="67">
-        <v>0</v>
-      </c>
-      <c r="K4" s="67">
-        <v>0</v>
-      </c>
-      <c r="L4" s="67">
-        <v>0</v>
-      </c>
-      <c r="M4" s="67">
-        <v>0</v>
-      </c>
-      <c r="N4" s="67">
-        <v>0</v>
-      </c>
-      <c r="O4" s="67">
-        <v>0</v>
-      </c>
-      <c r="P4" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="67">
-        <v>0</v>
-      </c>
-      <c r="R4" s="67">
-        <v>0</v>
-      </c>
-      <c r="S4" s="67">
-        <v>0</v>
-      </c>
-      <c r="T4" s="67">
-        <v>0</v>
-      </c>
-      <c r="U4" s="67">
-        <v>0</v>
-      </c>
-      <c r="V4" s="67">
-        <v>0</v>
-      </c>
-      <c r="W4" s="67">
-        <v>0</v>
-      </c>
-      <c r="X4" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="67">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="67">
-        <v>0</v>
-      </c>
-      <c r="C5" s="67">
-        <v>0</v>
-      </c>
-      <c r="D5" s="67">
-        <v>0</v>
-      </c>
-      <c r="E5" s="67">
-        <v>0</v>
-      </c>
-      <c r="F5" s="67">
-        <v>0</v>
-      </c>
-      <c r="G5" s="67">
-        <v>0</v>
-      </c>
-      <c r="H5" s="67">
-        <v>0</v>
-      </c>
-      <c r="I5" s="67">
-        <v>0</v>
-      </c>
-      <c r="J5" s="67">
-        <v>0</v>
-      </c>
-      <c r="K5" s="67">
-        <v>0</v>
-      </c>
-      <c r="L5" s="67">
-        <v>0</v>
-      </c>
-      <c r="M5" s="67">
-        <v>0</v>
-      </c>
-      <c r="N5" s="67">
-        <v>0</v>
-      </c>
-      <c r="O5" s="67">
-        <v>0</v>
-      </c>
-      <c r="P5" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="67">
-        <v>0</v>
-      </c>
-      <c r="R5" s="67">
-        <v>0</v>
-      </c>
-      <c r="S5" s="67">
-        <v>0</v>
-      </c>
-      <c r="T5" s="67">
-        <v>0</v>
-      </c>
-      <c r="U5" s="67">
-        <v>0</v>
-      </c>
-      <c r="V5" s="67">
-        <v>0</v>
-      </c>
-      <c r="W5" s="67">
-        <v>0</v>
-      </c>
-      <c r="X5" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="67">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="67">
-        <v>0</v>
-      </c>
-      <c r="C6" s="67">
-        <v>0</v>
-      </c>
-      <c r="D6" s="67">
-        <v>0</v>
-      </c>
-      <c r="E6" s="67">
-        <v>0</v>
-      </c>
-      <c r="F6" s="67">
-        <v>0</v>
-      </c>
-      <c r="G6" s="67">
-        <v>0</v>
-      </c>
-      <c r="H6" s="67">
-        <v>0</v>
-      </c>
-      <c r="I6" s="67">
-        <v>0</v>
-      </c>
-      <c r="J6" s="67">
-        <v>0</v>
-      </c>
-      <c r="K6" s="67">
-        <v>0</v>
-      </c>
-      <c r="L6" s="67">
-        <v>0</v>
-      </c>
-      <c r="M6" s="67">
-        <v>0</v>
-      </c>
-      <c r="N6" s="67">
-        <v>0</v>
-      </c>
-      <c r="O6" s="67">
-        <v>0</v>
-      </c>
-      <c r="P6" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="67">
-        <v>0</v>
-      </c>
-      <c r="R6" s="67">
-        <v>0</v>
-      </c>
-      <c r="S6" s="67">
-        <v>0</v>
-      </c>
-      <c r="T6" s="67">
-        <v>0</v>
-      </c>
-      <c r="U6" s="67">
-        <v>0</v>
-      </c>
-      <c r="V6" s="67">
-        <v>0</v>
-      </c>
-      <c r="W6" s="67">
-        <v>0</v>
-      </c>
-      <c r="X6" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="67">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="67" t="s">
+      <c r="A7" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="67">
-        <v>0</v>
-      </c>
-      <c r="C7" s="67">
-        <v>0</v>
-      </c>
-      <c r="D7" s="67">
-        <v>0</v>
-      </c>
-      <c r="E7" s="67">
-        <v>0</v>
-      </c>
-      <c r="F7" s="67">
-        <v>0</v>
-      </c>
-      <c r="G7" s="67">
-        <v>0</v>
-      </c>
-      <c r="H7" s="67">
-        <v>0</v>
-      </c>
-      <c r="I7" s="67">
-        <v>0</v>
-      </c>
-      <c r="J7" s="67">
-        <v>0</v>
-      </c>
-      <c r="K7" s="67">
-        <v>0</v>
-      </c>
-      <c r="L7" s="67">
-        <v>0</v>
-      </c>
-      <c r="M7" s="67">
-        <v>0</v>
-      </c>
-      <c r="N7" s="67">
-        <v>0</v>
-      </c>
-      <c r="O7" s="67">
-        <v>0</v>
-      </c>
-      <c r="P7" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="67">
-        <v>0</v>
-      </c>
-      <c r="R7" s="67">
-        <v>0</v>
-      </c>
-      <c r="S7" s="67">
-        <v>0</v>
-      </c>
-      <c r="T7" s="67">
-        <v>0</v>
-      </c>
-      <c r="U7" s="67">
-        <v>0</v>
-      </c>
-      <c r="V7" s="67">
-        <v>0</v>
-      </c>
-      <c r="W7" s="67">
-        <v>0</v>
-      </c>
-      <c r="X7" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="67">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="67" t="s">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="67">
-        <v>0</v>
-      </c>
-      <c r="C8" s="67">
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <f>'Inflation Reduction Act'!F32*Percent_Urban</f>
         <v>650.4654739739334</v>
       </c>
-      <c r="D8" s="67">
+      <c r="D8">
         <f>'Inflation Reduction Act'!G32*Percent_Urban</f>
         <v>650.4654739739334</v>
       </c>
-      <c r="E8" s="67">
+      <c r="E8">
         <f>'Inflation Reduction Act'!H32*Percent_Urban</f>
         <v>650.4654739739334</v>
       </c>
-      <c r="F8" s="67">
+      <c r="F8">
         <f>'Inflation Reduction Act'!I32*Percent_Urban</f>
         <v>650.4654739739334</v>
       </c>
-      <c r="G8" s="67">
+      <c r="G8">
         <f>'Inflation Reduction Act'!J32*Percent_Urban</f>
         <v>650.4654739739334</v>
       </c>
-      <c r="H8" s="67">
-        <v>0</v>
-      </c>
-      <c r="I8" s="67">
-        <v>0</v>
-      </c>
-      <c r="J8" s="67">
-        <v>0</v>
-      </c>
-      <c r="K8" s="67">
-        <v>0</v>
-      </c>
-      <c r="L8" s="67">
-        <v>0</v>
-      </c>
-      <c r="M8" s="67">
-        <v>0</v>
-      </c>
-      <c r="N8" s="67">
-        <v>0</v>
-      </c>
-      <c r="O8" s="67">
-        <v>0</v>
-      </c>
-      <c r="P8" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="67">
-        <v>0</v>
-      </c>
-      <c r="R8" s="67">
-        <v>0</v>
-      </c>
-      <c r="S8" s="67">
-        <v>0</v>
-      </c>
-      <c r="T8" s="67">
-        <v>0</v>
-      </c>
-      <c r="U8" s="67">
-        <v>0</v>
-      </c>
-      <c r="V8" s="67">
-        <v>0</v>
-      </c>
-      <c r="W8" s="67">
-        <v>0</v>
-      </c>
-      <c r="X8" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="67">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="67" t="s">
+      <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="67">
-        <v>0</v>
-      </c>
-      <c r="C9" s="67">
-        <v>0</v>
-      </c>
-      <c r="D9" s="67">
-        <v>0</v>
-      </c>
-      <c r="E9" s="67">
-        <v>0</v>
-      </c>
-      <c r="F9" s="67">
-        <v>0</v>
-      </c>
-      <c r="G9" s="67">
-        <v>0</v>
-      </c>
-      <c r="H9" s="67">
-        <v>0</v>
-      </c>
-      <c r="I9" s="67">
-        <v>0</v>
-      </c>
-      <c r="J9" s="67">
-        <v>0</v>
-      </c>
-      <c r="K9" s="67">
-        <v>0</v>
-      </c>
-      <c r="L9" s="67">
-        <v>0</v>
-      </c>
-      <c r="M9" s="67">
-        <v>0</v>
-      </c>
-      <c r="N9" s="67">
-        <v>0</v>
-      </c>
-      <c r="O9" s="67">
-        <v>0</v>
-      </c>
-      <c r="P9" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="67">
-        <v>0</v>
-      </c>
-      <c r="R9" s="67">
-        <v>0</v>
-      </c>
-      <c r="S9" s="67">
-        <v>0</v>
-      </c>
-      <c r="T9" s="67">
-        <v>0</v>
-      </c>
-      <c r="U9" s="67">
-        <v>0</v>
-      </c>
-      <c r="V9" s="67">
-        <v>0</v>
-      </c>
-      <c r="W9" s="67">
-        <v>0</v>
-      </c>
-      <c r="X9" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="67">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="67" t="s">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="67">
-        <v>0</v>
-      </c>
-      <c r="C10" s="67">
-        <v>0</v>
-      </c>
-      <c r="D10" s="67">
-        <v>0</v>
-      </c>
-      <c r="E10" s="67">
-        <v>0</v>
-      </c>
-      <c r="F10" s="67">
-        <v>0</v>
-      </c>
-      <c r="G10" s="67">
-        <v>0</v>
-      </c>
-      <c r="H10" s="67">
-        <v>0</v>
-      </c>
-      <c r="I10" s="67">
-        <v>0</v>
-      </c>
-      <c r="J10" s="67">
-        <v>0</v>
-      </c>
-      <c r="K10" s="67">
-        <v>0</v>
-      </c>
-      <c r="L10" s="67">
-        <v>0</v>
-      </c>
-      <c r="M10" s="67">
-        <v>0</v>
-      </c>
-      <c r="N10" s="67">
-        <v>0</v>
-      </c>
-      <c r="O10" s="67">
-        <v>0</v>
-      </c>
-      <c r="P10" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="67">
-        <v>0</v>
-      </c>
-      <c r="R10" s="67">
-        <v>0</v>
-      </c>
-      <c r="S10" s="67">
-        <v>0</v>
-      </c>
-      <c r="T10" s="67">
-        <v>0</v>
-      </c>
-      <c r="U10" s="67">
-        <v>0</v>
-      </c>
-      <c r="V10" s="67">
-        <v>0</v>
-      </c>
-      <c r="W10" s="67">
-        <v>0</v>
-      </c>
-      <c r="X10" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="67">
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="67" t="s">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="67">
-        <v>0</v>
-      </c>
-      <c r="C11" s="67">
-        <v>0</v>
-      </c>
-      <c r="D11" s="67">
-        <v>0</v>
-      </c>
-      <c r="E11" s="67">
-        <v>0</v>
-      </c>
-      <c r="F11" s="67">
-        <v>0</v>
-      </c>
-      <c r="G11" s="67">
-        <v>0</v>
-      </c>
-      <c r="H11" s="67">
-        <v>0</v>
-      </c>
-      <c r="I11" s="67">
-        <v>0</v>
-      </c>
-      <c r="J11" s="67">
-        <v>0</v>
-      </c>
-      <c r="K11" s="67">
-        <v>0</v>
-      </c>
-      <c r="L11" s="67">
-        <v>0</v>
-      </c>
-      <c r="M11" s="67">
-        <v>0</v>
-      </c>
-      <c r="N11" s="67">
-        <v>0</v>
-      </c>
-      <c r="O11" s="67">
-        <v>0</v>
-      </c>
-      <c r="P11" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="67">
-        <v>0</v>
-      </c>
-      <c r="R11" s="67">
-        <v>0</v>
-      </c>
-      <c r="S11" s="67">
-        <v>0</v>
-      </c>
-      <c r="T11" s="67">
-        <v>0</v>
-      </c>
-      <c r="U11" s="67">
-        <v>0</v>
-      </c>
-      <c r="V11" s="67">
-        <v>0</v>
-      </c>
-      <c r="W11" s="67">
-        <v>0</v>
-      </c>
-      <c r="X11" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="67">
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="67" t="s">
+      <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="67">
-        <v>0</v>
-      </c>
-      <c r="C12" s="67">
-        <v>0</v>
-      </c>
-      <c r="D12" s="67">
-        <v>0</v>
-      </c>
-      <c r="E12" s="67">
-        <v>0</v>
-      </c>
-      <c r="F12" s="67">
-        <v>0</v>
-      </c>
-      <c r="G12" s="67">
-        <v>0</v>
-      </c>
-      <c r="H12" s="67">
-        <v>0</v>
-      </c>
-      <c r="I12" s="67">
-        <v>0</v>
-      </c>
-      <c r="J12" s="67">
-        <v>0</v>
-      </c>
-      <c r="K12" s="67">
-        <v>0</v>
-      </c>
-      <c r="L12" s="67">
-        <v>0</v>
-      </c>
-      <c r="M12" s="67">
-        <v>0</v>
-      </c>
-      <c r="N12" s="67">
-        <v>0</v>
-      </c>
-      <c r="O12" s="67">
-        <v>0</v>
-      </c>
-      <c r="P12" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="67">
-        <v>0</v>
-      </c>
-      <c r="R12" s="67">
-        <v>0</v>
-      </c>
-      <c r="S12" s="67">
-        <v>0</v>
-      </c>
-      <c r="T12" s="67">
-        <v>0</v>
-      </c>
-      <c r="U12" s="67">
-        <v>0</v>
-      </c>
-      <c r="V12" s="67">
-        <v>0</v>
-      </c>
-      <c r="W12" s="67">
-        <v>0</v>
-      </c>
-      <c r="X12" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="67">
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="67" t="s">
+      <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="67">
-        <v>0</v>
-      </c>
-      <c r="C13" s="67">
-        <v>0</v>
-      </c>
-      <c r="D13" s="67">
-        <v>0</v>
-      </c>
-      <c r="E13" s="67">
-        <v>0</v>
-      </c>
-      <c r="F13" s="67">
-        <v>0</v>
-      </c>
-      <c r="G13" s="67">
-        <v>0</v>
-      </c>
-      <c r="H13" s="67">
-        <v>0</v>
-      </c>
-      <c r="I13" s="67">
-        <v>0</v>
-      </c>
-      <c r="J13" s="67">
-        <v>0</v>
-      </c>
-      <c r="K13" s="67">
-        <v>0</v>
-      </c>
-      <c r="L13" s="67">
-        <v>0</v>
-      </c>
-      <c r="M13" s="67">
-        <v>0</v>
-      </c>
-      <c r="N13" s="67">
-        <v>0</v>
-      </c>
-      <c r="O13" s="67">
-        <v>0</v>
-      </c>
-      <c r="P13" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="67">
-        <v>0</v>
-      </c>
-      <c r="R13" s="67">
-        <v>0</v>
-      </c>
-      <c r="S13" s="67">
-        <v>0</v>
-      </c>
-      <c r="T13" s="67">
-        <v>0</v>
-      </c>
-      <c r="U13" s="67">
-        <v>0</v>
-      </c>
-      <c r="V13" s="67">
-        <v>0</v>
-      </c>
-      <c r="W13" s="67">
-        <v>0</v>
-      </c>
-      <c r="X13" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="67">
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="67" t="s">
+      <c r="A14" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="67">
-        <v>0</v>
-      </c>
-      <c r="C14" s="67">
-        <v>0</v>
-      </c>
-      <c r="D14" s="67">
-        <v>0</v>
-      </c>
-      <c r="E14" s="67">
-        <v>0</v>
-      </c>
-      <c r="F14" s="67">
-        <v>0</v>
-      </c>
-      <c r="G14" s="67">
-        <v>0</v>
-      </c>
-      <c r="H14" s="67">
-        <v>0</v>
-      </c>
-      <c r="I14" s="67">
-        <v>0</v>
-      </c>
-      <c r="J14" s="67">
-        <v>0</v>
-      </c>
-      <c r="K14" s="67">
-        <v>0</v>
-      </c>
-      <c r="L14" s="67">
-        <v>0</v>
-      </c>
-      <c r="M14" s="67">
-        <v>0</v>
-      </c>
-      <c r="N14" s="67">
-        <v>0</v>
-      </c>
-      <c r="O14" s="67">
-        <v>0</v>
-      </c>
-      <c r="P14" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="67">
-        <v>0</v>
-      </c>
-      <c r="R14" s="67">
-        <v>0</v>
-      </c>
-      <c r="S14" s="67">
-        <v>0</v>
-      </c>
-      <c r="T14" s="67">
-        <v>0</v>
-      </c>
-      <c r="U14" s="67">
-        <v>0</v>
-      </c>
-      <c r="V14" s="67">
-        <v>0</v>
-      </c>
-      <c r="W14" s="67">
-        <v>0</v>
-      </c>
-      <c r="X14" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="67">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="67" t="s">
+      <c r="A15" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="67">
-        <v>0</v>
-      </c>
-      <c r="C15" s="67">
-        <v>0</v>
-      </c>
-      <c r="D15" s="67">
-        <v>0</v>
-      </c>
-      <c r="E15" s="67">
-        <v>0</v>
-      </c>
-      <c r="F15" s="67">
-        <v>0</v>
-      </c>
-      <c r="G15" s="67">
-        <v>0</v>
-      </c>
-      <c r="H15" s="67">
-        <v>0</v>
-      </c>
-      <c r="I15" s="67">
-        <v>0</v>
-      </c>
-      <c r="J15" s="67">
-        <v>0</v>
-      </c>
-      <c r="K15" s="67">
-        <v>0</v>
-      </c>
-      <c r="L15" s="67">
-        <v>0</v>
-      </c>
-      <c r="M15" s="67">
-        <v>0</v>
-      </c>
-      <c r="N15" s="67">
-        <v>0</v>
-      </c>
-      <c r="O15" s="67">
-        <v>0</v>
-      </c>
-      <c r="P15" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="67">
-        <v>0</v>
-      </c>
-      <c r="R15" s="67">
-        <v>0</v>
-      </c>
-      <c r="S15" s="67">
-        <v>0</v>
-      </c>
-      <c r="T15" s="67">
-        <v>0</v>
-      </c>
-      <c r="U15" s="67">
-        <v>0</v>
-      </c>
-      <c r="V15" s="67">
-        <v>0</v>
-      </c>
-      <c r="W15" s="67">
-        <v>0</v>
-      </c>
-      <c r="X15" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="67">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="67" t="s">
+      <c r="A16" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="67">
-        <v>0</v>
-      </c>
-      <c r="C16" s="67">
-        <v>0</v>
-      </c>
-      <c r="D16" s="67">
-        <v>0</v>
-      </c>
-      <c r="E16" s="67">
-        <v>0</v>
-      </c>
-      <c r="F16" s="67">
-        <v>0</v>
-      </c>
-      <c r="G16" s="67">
-        <v>0</v>
-      </c>
-      <c r="H16" s="67">
-        <v>0</v>
-      </c>
-      <c r="I16" s="67">
-        <v>0</v>
-      </c>
-      <c r="J16" s="67">
-        <v>0</v>
-      </c>
-      <c r="K16" s="67">
-        <v>0</v>
-      </c>
-      <c r="L16" s="67">
-        <v>0</v>
-      </c>
-      <c r="M16" s="67">
-        <v>0</v>
-      </c>
-      <c r="N16" s="67">
-        <v>0</v>
-      </c>
-      <c r="O16" s="67">
-        <v>0</v>
-      </c>
-      <c r="P16" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="67">
-        <v>0</v>
-      </c>
-      <c r="R16" s="67">
-        <v>0</v>
-      </c>
-      <c r="S16" s="67">
-        <v>0</v>
-      </c>
-      <c r="T16" s="67">
-        <v>0</v>
-      </c>
-      <c r="U16" s="67">
-        <v>0</v>
-      </c>
-      <c r="V16" s="67">
-        <v>0</v>
-      </c>
-      <c r="W16" s="67">
-        <v>0</v>
-      </c>
-      <c r="X16" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="67">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="67" t="s">
+      <c r="A17" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="67">
-        <v>0</v>
-      </c>
-      <c r="C17" s="67">
-        <v>0</v>
-      </c>
-      <c r="D17" s="67">
-        <v>0</v>
-      </c>
-      <c r="E17" s="67">
-        <v>0</v>
-      </c>
-      <c r="F17" s="67">
-        <v>0</v>
-      </c>
-      <c r="G17" s="67">
-        <v>0</v>
-      </c>
-      <c r="H17" s="67">
-        <v>0</v>
-      </c>
-      <c r="I17" s="67">
-        <v>0</v>
-      </c>
-      <c r="J17" s="67">
-        <v>0</v>
-      </c>
-      <c r="K17" s="67">
-        <v>0</v>
-      </c>
-      <c r="L17" s="67">
-        <v>0</v>
-      </c>
-      <c r="M17" s="67">
-        <v>0</v>
-      </c>
-      <c r="N17" s="67">
-        <v>0</v>
-      </c>
-      <c r="O17" s="67">
-        <v>0</v>
-      </c>
-      <c r="P17" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="67">
-        <v>0</v>
-      </c>
-      <c r="R17" s="67">
-        <v>0</v>
-      </c>
-      <c r="S17" s="67">
-        <v>0</v>
-      </c>
-      <c r="T17" s="67">
-        <v>0</v>
-      </c>
-      <c r="U17" s="67">
-        <v>0</v>
-      </c>
-      <c r="V17" s="67">
-        <v>0</v>
-      </c>
-      <c r="W17" s="67">
-        <v>0</v>
-      </c>
-      <c r="X17" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="67">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="67" t="s">
+      <c r="A18" t="s">
         <v>160</v>
       </c>
-      <c r="B18" s="67">
-        <v>0</v>
-      </c>
-      <c r="C18" s="67">
-        <v>0</v>
-      </c>
-      <c r="D18" s="67">
-        <v>0</v>
-      </c>
-      <c r="E18" s="67">
-        <v>0</v>
-      </c>
-      <c r="F18" s="67">
-        <v>0</v>
-      </c>
-      <c r="G18" s="67">
-        <v>0</v>
-      </c>
-      <c r="H18" s="67">
-        <v>0</v>
-      </c>
-      <c r="I18" s="67">
-        <v>0</v>
-      </c>
-      <c r="J18" s="67">
-        <v>0</v>
-      </c>
-      <c r="K18" s="67">
-        <v>0</v>
-      </c>
-      <c r="L18" s="67">
-        <v>0</v>
-      </c>
-      <c r="M18" s="67">
-        <v>0</v>
-      </c>
-      <c r="N18" s="67">
-        <v>0</v>
-      </c>
-      <c r="O18" s="67">
-        <v>0</v>
-      </c>
-      <c r="P18" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="67">
-        <v>0</v>
-      </c>
-      <c r="R18" s="67">
-        <v>0</v>
-      </c>
-      <c r="S18" s="67">
-        <v>0</v>
-      </c>
-      <c r="T18" s="67">
-        <v>0</v>
-      </c>
-      <c r="U18" s="67">
-        <v>0</v>
-      </c>
-      <c r="V18" s="67">
-        <v>0</v>
-      </c>
-      <c r="W18" s="67">
-        <v>0</v>
-      </c>
-      <c r="X18" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="67">
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="55" t="s">
         <v>328</v>
       </c>
-      <c r="B19" s="67">
-        <v>0</v>
-      </c>
-      <c r="C19" s="67">
-        <v>0</v>
-      </c>
-      <c r="D19" s="67">
-        <v>0</v>
-      </c>
-      <c r="E19" s="67">
-        <v>0</v>
-      </c>
-      <c r="F19" s="67">
-        <v>0</v>
-      </c>
-      <c r="G19" s="67">
-        <v>0</v>
-      </c>
-      <c r="H19" s="67">
-        <v>0</v>
-      </c>
-      <c r="I19" s="67">
-        <v>0</v>
-      </c>
-      <c r="J19" s="67">
-        <v>0</v>
-      </c>
-      <c r="K19" s="67">
-        <v>0</v>
-      </c>
-      <c r="L19" s="67">
-        <v>0</v>
-      </c>
-      <c r="M19" s="67">
-        <v>0</v>
-      </c>
-      <c r="N19" s="67">
-        <v>0</v>
-      </c>
-      <c r="O19" s="67">
-        <v>0</v>
-      </c>
-      <c r="P19" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="67">
-        <v>0</v>
-      </c>
-      <c r="R19" s="67">
-        <v>0</v>
-      </c>
-      <c r="S19" s="67">
-        <v>0</v>
-      </c>
-      <c r="T19" s="67">
-        <v>0</v>
-      </c>
-      <c r="U19" s="67">
-        <v>0</v>
-      </c>
-      <c r="V19" s="67">
-        <v>0</v>
-      </c>
-      <c r="W19" s="67">
-        <v>0</v>
-      </c>
-      <c r="X19" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="67">
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="55" t="s">
         <v>329</v>
       </c>
-      <c r="B20" s="67">
-        <v>0</v>
-      </c>
-      <c r="C20" s="67">
-        <v>0</v>
-      </c>
-      <c r="D20" s="67">
-        <v>0</v>
-      </c>
-      <c r="E20" s="67">
-        <v>0</v>
-      </c>
-      <c r="F20" s="67">
-        <v>0</v>
-      </c>
-      <c r="G20" s="67">
-        <v>0</v>
-      </c>
-      <c r="H20" s="67">
-        <v>0</v>
-      </c>
-      <c r="I20" s="67">
-        <v>0</v>
-      </c>
-      <c r="J20" s="67">
-        <v>0</v>
-      </c>
-      <c r="K20" s="67">
-        <v>0</v>
-      </c>
-      <c r="L20" s="67">
-        <v>0</v>
-      </c>
-      <c r="M20" s="67">
-        <v>0</v>
-      </c>
-      <c r="N20" s="67">
-        <v>0</v>
-      </c>
-      <c r="O20" s="67">
-        <v>0</v>
-      </c>
-      <c r="P20" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="67">
-        <v>0</v>
-      </c>
-      <c r="R20" s="67">
-        <v>0</v>
-      </c>
-      <c r="S20" s="67">
-        <v>0</v>
-      </c>
-      <c r="T20" s="67">
-        <v>0</v>
-      </c>
-      <c r="U20" s="67">
-        <v>0</v>
-      </c>
-      <c r="V20" s="67">
-        <v>0</v>
-      </c>
-      <c r="W20" s="67">
-        <v>0</v>
-      </c>
-      <c r="X20" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="67">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="B21" s="67">
-        <v>0</v>
-      </c>
-      <c r="C21" s="67">
-        <v>0</v>
-      </c>
-      <c r="D21" s="67">
-        <v>0</v>
-      </c>
-      <c r="E21" s="67">
-        <v>0</v>
-      </c>
-      <c r="F21" s="67">
-        <v>0</v>
-      </c>
-      <c r="G21" s="67">
-        <v>0</v>
-      </c>
-      <c r="H21" s="67">
-        <v>0</v>
-      </c>
-      <c r="I21" s="67">
-        <v>0</v>
-      </c>
-      <c r="J21" s="67">
-        <v>0</v>
-      </c>
-      <c r="K21" s="67">
-        <v>0</v>
-      </c>
-      <c r="L21" s="67">
-        <v>0</v>
-      </c>
-      <c r="M21" s="67">
-        <v>0</v>
-      </c>
-      <c r="N21" s="67">
-        <v>0</v>
-      </c>
-      <c r="O21" s="67">
-        <v>0</v>
-      </c>
-      <c r="P21" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="67">
-        <v>0</v>
-      </c>
-      <c r="R21" s="67">
-        <v>0</v>
-      </c>
-      <c r="S21" s="67">
-        <v>0</v>
-      </c>
-      <c r="T21" s="67">
-        <v>0</v>
-      </c>
-      <c r="U21" s="67">
-        <v>0</v>
-      </c>
-      <c r="V21" s="67">
-        <v>0</v>
-      </c>
-      <c r="W21" s="67">
-        <v>0</v>
-      </c>
-      <c r="X21" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="67">
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="68" t="s">
+      <c r="A22" s="55" t="s">
         <v>331</v>
       </c>
-      <c r="B22" s="67">
-        <v>0</v>
-      </c>
-      <c r="C22" s="67">
-        <v>0</v>
-      </c>
-      <c r="D22" s="67">
-        <v>0</v>
-      </c>
-      <c r="E22" s="67">
-        <v>0</v>
-      </c>
-      <c r="F22" s="67">
-        <v>0</v>
-      </c>
-      <c r="G22" s="67">
-        <v>0</v>
-      </c>
-      <c r="H22" s="67">
-        <v>0</v>
-      </c>
-      <c r="I22" s="67">
-        <v>0</v>
-      </c>
-      <c r="J22" s="67">
-        <v>0</v>
-      </c>
-      <c r="K22" s="67">
-        <v>0</v>
-      </c>
-      <c r="L22" s="67">
-        <v>0</v>
-      </c>
-      <c r="M22" s="67">
-        <v>0</v>
-      </c>
-      <c r="N22" s="67">
-        <v>0</v>
-      </c>
-      <c r="O22" s="67">
-        <v>0</v>
-      </c>
-      <c r="P22" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="67">
-        <v>0</v>
-      </c>
-      <c r="R22" s="67">
-        <v>0</v>
-      </c>
-      <c r="S22" s="67">
-        <v>0</v>
-      </c>
-      <c r="T22" s="67">
-        <v>0</v>
-      </c>
-      <c r="U22" s="67">
-        <v>0</v>
-      </c>
-      <c r="V22" s="67">
-        <v>0</v>
-      </c>
-      <c r="W22" s="67">
-        <v>0</v>
-      </c>
-      <c r="X22" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="67">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="55" t="s">
         <v>332</v>
       </c>
-      <c r="B23" s="67">
-        <v>0</v>
-      </c>
-      <c r="C23" s="67">
-        <v>0</v>
-      </c>
-      <c r="D23" s="67">
-        <v>0</v>
-      </c>
-      <c r="E23" s="67">
-        <v>0</v>
-      </c>
-      <c r="F23" s="67">
-        <v>0</v>
-      </c>
-      <c r="G23" s="67">
-        <v>0</v>
-      </c>
-      <c r="H23" s="67">
-        <v>0</v>
-      </c>
-      <c r="I23" s="67">
-        <v>0</v>
-      </c>
-      <c r="J23" s="67">
-        <v>0</v>
-      </c>
-      <c r="K23" s="67">
-        <v>0</v>
-      </c>
-      <c r="L23" s="67">
-        <v>0</v>
-      </c>
-      <c r="M23" s="67">
-        <v>0</v>
-      </c>
-      <c r="N23" s="67">
-        <v>0</v>
-      </c>
-      <c r="O23" s="67">
-        <v>0</v>
-      </c>
-      <c r="P23" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="67">
-        <v>0</v>
-      </c>
-      <c r="R23" s="67">
-        <v>0</v>
-      </c>
-      <c r="S23" s="67">
-        <v>0</v>
-      </c>
-      <c r="T23" s="67">
-        <v>0</v>
-      </c>
-      <c r="U23" s="67">
-        <v>0</v>
-      </c>
-      <c r="V23" s="67">
-        <v>0</v>
-      </c>
-      <c r="W23" s="67">
-        <v>0</v>
-      </c>
-      <c r="X23" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="67">
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="69" t="s">
+      <c r="A24" s="56" t="s">
         <v>333</v>
       </c>
-      <c r="B24" s="67">
-        <v>0</v>
-      </c>
-      <c r="C24" s="67">
-        <v>0</v>
-      </c>
-      <c r="D24" s="67">
-        <v>0</v>
-      </c>
-      <c r="E24" s="67">
-        <v>0</v>
-      </c>
-      <c r="F24" s="67">
-        <v>0</v>
-      </c>
-      <c r="G24" s="67">
-        <v>0</v>
-      </c>
-      <c r="H24" s="67">
-        <v>0</v>
-      </c>
-      <c r="I24" s="67">
-        <v>0</v>
-      </c>
-      <c r="J24" s="67">
-        <v>0</v>
-      </c>
-      <c r="K24" s="67">
-        <v>0</v>
-      </c>
-      <c r="L24" s="67">
-        <v>0</v>
-      </c>
-      <c r="M24" s="67">
-        <v>0</v>
-      </c>
-      <c r="N24" s="67">
-        <v>0</v>
-      </c>
-      <c r="O24" s="67">
-        <v>0</v>
-      </c>
-      <c r="P24" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="67">
-        <v>0</v>
-      </c>
-      <c r="R24" s="67">
-        <v>0</v>
-      </c>
-      <c r="S24" s="67">
-        <v>0</v>
-      </c>
-      <c r="T24" s="67">
-        <v>0</v>
-      </c>
-      <c r="U24" s="67">
-        <v>0</v>
-      </c>
-      <c r="V24" s="67">
-        <v>0</v>
-      </c>
-      <c r="W24" s="67">
-        <v>0</v>
-      </c>
-      <c r="X24" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="67">
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="69" t="s">
+      <c r="A25" s="56" t="s">
         <v>334</v>
       </c>
-      <c r="B25" s="67">
-        <v>0</v>
-      </c>
-      <c r="C25" s="67">
-        <v>0</v>
-      </c>
-      <c r="D25" s="67">
-        <v>0</v>
-      </c>
-      <c r="E25" s="67">
-        <v>0</v>
-      </c>
-      <c r="F25" s="67">
-        <v>0</v>
-      </c>
-      <c r="G25" s="67">
-        <v>0</v>
-      </c>
-      <c r="H25" s="67">
-        <v>0</v>
-      </c>
-      <c r="I25" s="67">
-        <v>0</v>
-      </c>
-      <c r="J25" s="67">
-        <v>0</v>
-      </c>
-      <c r="K25" s="67">
-        <v>0</v>
-      </c>
-      <c r="L25" s="67">
-        <v>0</v>
-      </c>
-      <c r="M25" s="67">
-        <v>0</v>
-      </c>
-      <c r="N25" s="67">
-        <v>0</v>
-      </c>
-      <c r="O25" s="67">
-        <v>0</v>
-      </c>
-      <c r="P25" s="67">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="67">
-        <v>0</v>
-      </c>
-      <c r="R25" s="67">
-        <v>0</v>
-      </c>
-      <c r="S25" s="67">
-        <v>0</v>
-      </c>
-      <c r="T25" s="67">
-        <v>0</v>
-      </c>
-      <c r="U25" s="67">
-        <v>0</v>
-      </c>
-      <c r="V25" s="67">
-        <v>0</v>
-      </c>
-      <c r="W25" s="67">
-        <v>0</v>
-      </c>
-      <c r="X25" s="67">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="67">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="67">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="67">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="67">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
         <v>0</v>
       </c>
     </row>
@@ -30142,6 +30157,2169 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E247739E-3FF7-405C-AC36-79FD8625BF19}">
+  <sheetPr>
+    <tabColor rgb="FF1F3864"/>
+  </sheetPr>
+  <dimension ref="A1:AB25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>328</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>329</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>330</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>331</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>332</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>333</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>334</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC83FA4-A821-4676-A3D4-0EB58B853D28}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -35776,7 +37954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DFD15FE-7663-4FED-9BC8-C5758E4A9992}">
   <sheetPr>
     <tabColor theme="3"/>
